--- a/extenbooks/XS003_extenbook.xlsx
+++ b/extenbooks/XS003_extenbook.xlsx
@@ -14116,7 +14116,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-02T06:26:36.666169+00:00</t>
+          <t>2026-07-11T03:44:27.341166+00:00</t>
         </is>
       </c>
     </row>
@@ -14131,11 +14131,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14158,6 +14158,162 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SHAIKH_APPENDIX_6_8</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>book_period_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pipeline_consistent</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "HEADLINE MIXED-UNITS FIX. Series interleaves two genuinely different quantities: three dollar imputed-interest adjustments (A-C, billions, can be negative) and four decimal profit rates (D-G, ~0.03-0.19). Under the banned series-level 'mixed_billions_usd_and_decimal_rates' string it rendered as one nonsensical spiky line (the canonical AS003/XS003 failure in UNITS_VALIDATION_STANDARD) and fails gate P14. After per-subseries units the A-C dollar panel and the D-G rate panel each render sensibly one-trace-per-subseries. These corrected profit rates are the empirical objects feeding S601-S604 and Ch16 dynamics.", "date": "2026-06-10"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/XS003_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/XS003_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>FISIM-revision-stable T7.11 line resolver used (see _nipa_t711_line_resolver.py). Source: Appendix Tables 6.8.I.3 + 6.8.II.7. Used by S601, S602, S603, S604.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>per_subseries</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
